--- a/05_14_26 Dollar General LBO.xlsx
+++ b/05_14_26 Dollar General LBO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\troyr\Documents\Finance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\troyr\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C4DCED-DCB1-4351-AC00-C6E1F725F920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248D9A5E-A085-4641-8337-AAB805BEA18E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{33A884AF-7A56-4D34-836C-67DEC903C3E5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{33A884AF-7A56-4D34-836C-67DEC903C3E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -542,7 +542,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="3"/>
@@ -559,11 +559,8 @@
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
@@ -647,6 +644,13 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="6" fillId="3" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="8">
     <cellStyle name="Comma 2" xfId="4" xr:uid="{FE387761-5A72-4BC1-A066-2445D7E96A2A}"/>
@@ -1017,185 +1021,185 @@
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
+      <c r="A4" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="40"/>
-      <c r="C4" s="40"/>
-      <c r="E4" s="40" t="s">
+      <c r="B4" s="37"/>
+      <c r="C4" s="37"/>
+      <c r="E4" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="40"/>
-      <c r="G4" s="42" t="s">
+      <c r="F4" s="37"/>
+      <c r="G4" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="43"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="43" t="s">
+      <c r="H4" s="40"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="44"/>
-      <c r="P4" s="42" t="s">
+      <c r="K4" s="40"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="40"/>
+      <c r="N4" s="41"/>
+      <c r="P4" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="44"/>
+      <c r="Q4" s="40"/>
+      <c r="R4" s="41"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A5" s="62" t="s">
+      <c r="A5" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="63"/>
+      <c r="B5" s="60"/>
       <c r="C5" s="12">
         <v>1512311</v>
       </c>
       <c r="E5" s="9"/>
-      <c r="G5" s="59">
+      <c r="G5" s="56">
         <v>2023</v>
       </c>
-      <c r="H5" s="60">
+      <c r="H5" s="57">
         <v>2024</v>
       </c>
-      <c r="I5" s="61">
+      <c r="I5" s="58">
         <v>2025</v>
       </c>
-      <c r="J5" s="60">
+      <c r="J5" s="57">
         <v>2026</v>
       </c>
-      <c r="K5" s="60">
+      <c r="K5" s="57">
         <v>2027</v>
       </c>
-      <c r="L5" s="60">
+      <c r="L5" s="57">
         <v>2028</v>
       </c>
-      <c r="M5" s="60">
+      <c r="M5" s="57">
         <v>2029</v>
       </c>
-      <c r="N5" s="61">
+      <c r="N5" s="58">
         <v>2030</v>
       </c>
-      <c r="P5" s="95" t="s">
+      <c r="P5" s="92" t="s">
         <v>53</v>
       </c>
-      <c r="Q5" s="96"/>
-      <c r="R5" s="31">
+      <c r="Q5" s="93"/>
+      <c r="R5" s="28">
         <f>C26</f>
         <v>9.7029274232086173</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="65"/>
+      <c r="B6" s="62"/>
       <c r="C6" s="12">
         <v>452281</v>
       </c>
-      <c r="E6" s="62" t="s">
+      <c r="E6" s="59" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="63"/>
-      <c r="G6" s="45">
+      <c r="F6" s="60"/>
+      <c r="G6" s="42">
         <v>38691609</v>
       </c>
-      <c r="H6" s="46">
+      <c r="H6" s="43">
         <v>40612308</v>
       </c>
-      <c r="I6" s="47">
+      <c r="I6" s="44">
         <v>42724369</v>
       </c>
-      <c r="J6" s="46">
+      <c r="J6" s="43">
         <f>I6*(1+J25)</f>
         <v>44895763.912330776</v>
       </c>
-      <c r="K6" s="46">
+      <c r="K6" s="43">
         <f>J6*(1+K25)</f>
         <v>47177516.355402283</v>
       </c>
-      <c r="L6" s="46">
+      <c r="L6" s="43">
         <f>K6*(1+L25)</f>
         <v>49575235.066953585</v>
       </c>
-      <c r="M6" s="46">
+      <c r="M6" s="43">
         <f>L6*(1+M25)</f>
         <v>52094813.83947999</v>
       </c>
-      <c r="N6" s="47">
+      <c r="N6" s="44">
         <f>M6*(1+N25)</f>
         <v>54742446.007666387</v>
       </c>
-      <c r="P6" s="64" t="s">
+      <c r="P6" s="61" t="s">
         <v>54</v>
       </c>
-      <c r="Q6" s="65"/>
-      <c r="R6" s="17">
+      <c r="Q6" s="62"/>
+      <c r="R6" s="16">
         <f>N7</f>
         <v>4153282.630285129</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="65"/>
+      <c r="B7" s="62"/>
       <c r="C7" s="12">
         <v>230567</v>
       </c>
-      <c r="E7" s="82" t="s">
+      <c r="E7" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="83"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="93"/>
-      <c r="I7" s="94">
+      <c r="F7" s="80"/>
+      <c r="G7" s="89"/>
+      <c r="H7" s="90"/>
+      <c r="I7" s="91">
         <f>C9</f>
         <v>3241477</v>
       </c>
-      <c r="J7" s="93">
+      <c r="J7" s="90">
         <f t="shared" ref="J7:N8" si="0">J26*J$6</f>
         <v>3406219.671009073</v>
       </c>
-      <c r="K7" s="93">
+      <c r="K7" s="90">
         <f t="shared" si="0"/>
         <v>3579335.113952422</v>
       </c>
-      <c r="L7" s="93">
+      <c r="L7" s="90">
         <f t="shared" si="0"/>
         <v>3761248.8610217627</v>
       </c>
-      <c r="M7" s="93">
+      <c r="M7" s="90">
         <f t="shared" si="0"/>
         <v>3952408.0713738822</v>
       </c>
-      <c r="N7" s="94">
+      <c r="N7" s="91">
         <f t="shared" si="0"/>
         <v>4153282.630285129</v>
       </c>
-      <c r="P7" s="64" t="s">
+      <c r="P7" s="61" t="s">
         <v>55</v>
       </c>
-      <c r="Q7" s="65"/>
-      <c r="R7" s="17">
+      <c r="Q7" s="62"/>
+      <c r="R7" s="16">
         <f>R6*R5</f>
         <v>40298999.929729596</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="65"/>
+      <c r="B8" s="62"/>
       <c r="C8" s="12">
         <v>1046318</v>
       </c>
-      <c r="E8" s="64" t="s">
+      <c r="E8" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="65"/>
-      <c r="G8" s="34">
+      <c r="F8" s="62"/>
+      <c r="G8" s="31">
         <v>848793</v>
       </c>
       <c r="H8" s="11">
@@ -1224,29 +1228,29 @@
         <f t="shared" si="0"/>
         <v>1283777.2944073423</v>
       </c>
-      <c r="P8" s="64" t="s">
+      <c r="P8" s="61" t="s">
         <v>59</v>
       </c>
-      <c r="Q8" s="65"/>
-      <c r="R8" s="17">
+      <c r="Q8" s="62"/>
+      <c r="R8" s="16">
         <f>N36</f>
         <v>5232630.2734031565</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A9" s="64" t="s">
+      <c r="A9" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="65"/>
+      <c r="B9" s="62"/>
       <c r="C9" s="12">
         <f>SUM(C5:C8)</f>
         <v>3241477</v>
       </c>
-      <c r="E9" s="64" t="s">
+      <c r="E9" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="65"/>
-      <c r="G9" s="34"/>
+      <c r="F9" s="62"/>
+      <c r="G9" s="31"/>
       <c r="H9" s="11"/>
       <c r="I9" s="12">
         <f>I7-I8</f>
@@ -1272,24 +1276,24 @@
         <f t="shared" si="1"/>
         <v>2869505.3358777864</v>
       </c>
-      <c r="P9" s="82" t="s">
+      <c r="P9" s="79" t="s">
         <v>56</v>
       </c>
-      <c r="Q9" s="83"/>
-      <c r="R9" s="84">
+      <c r="Q9" s="80"/>
+      <c r="R9" s="81">
         <f>R7-R8</f>
         <v>35066369.656326443</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A10" s="64"/>
-      <c r="B10" s="65"/>
+      <c r="A10" s="61"/>
+      <c r="B10" s="62"/>
       <c r="C10" s="10"/>
-      <c r="E10" s="64" t="s">
+      <c r="E10" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="65"/>
-      <c r="G10" s="34"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="31"/>
       <c r="H10" s="11"/>
       <c r="I10" s="12">
         <f>C7</f>
@@ -1315,28 +1319,28 @@
         <f>N38</f>
         <v>648283.40275187371</v>
       </c>
-      <c r="P10" s="82" t="s">
+      <c r="P10" s="79" t="s">
         <v>58</v>
       </c>
-      <c r="Q10" s="83"/>
-      <c r="R10" s="89">
+      <c r="Q10" s="80"/>
+      <c r="R10" s="86">
         <f>R9/C35</f>
         <v>2.0044562104612043</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A11" s="64" t="s">
+      <c r="A11" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="65"/>
+      <c r="B11" s="62"/>
       <c r="C11" s="12">
         <v>14401</v>
       </c>
-      <c r="E11" s="64" t="s">
+      <c r="E11" s="61" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="65"/>
-      <c r="G11" s="34"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="31"/>
       <c r="H11" s="11"/>
       <c r="I11" s="12">
         <f>I9-I10</f>
@@ -1362,28 +1366,28 @@
         <f t="shared" si="2"/>
         <v>2221221.9331259127</v>
       </c>
-      <c r="P11" s="85" t="s">
+      <c r="P11" s="82" t="s">
         <v>57</v>
       </c>
-      <c r="Q11" s="86"/>
-      <c r="R11" s="90">
+      <c r="Q11" s="83"/>
+      <c r="R11" s="87">
         <f>R10^(1/5) - 1</f>
         <v>0.14920978355589787</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A12" s="64" t="s">
+      <c r="A12" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="65"/>
+      <c r="B12" s="62"/>
       <c r="C12" s="12">
         <v>4565881</v>
       </c>
-      <c r="E12" s="64" t="s">
+      <c r="E12" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="65"/>
-      <c r="G12" s="34"/>
+      <c r="F12" s="62"/>
+      <c r="G12" s="31"/>
       <c r="H12" s="11"/>
       <c r="I12" s="12">
         <v>452281</v>
@@ -1410,166 +1414,166 @@
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A13" s="64" t="s">
+      <c r="A13" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="65"/>
+      <c r="B13" s="62"/>
       <c r="C13" s="12">
         <f>C11+C12</f>
         <v>4580282</v>
       </c>
-      <c r="E13" s="66" t="s">
+      <c r="E13" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="F13" s="67"/>
-      <c r="G13" s="48"/>
-      <c r="H13" s="49"/>
-      <c r="I13" s="27">
+      <c r="F13" s="64"/>
+      <c r="G13" s="45"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="24">
         <f>I11-I12</f>
         <v>1512311</v>
       </c>
-      <c r="J13" s="49">
+      <c r="J13" s="46">
         <f>J11-J12</f>
         <v>857149.71112547396</v>
       </c>
-      <c r="K13" s="49">
+      <c r="K13" s="46">
         <f t="shared" ref="K13:N13" si="3">K11-K12</f>
         <v>1040313.0395303394</v>
       </c>
-      <c r="L13" s="49">
+      <c r="L13" s="46">
         <f t="shared" si="3"/>
         <v>1242404.6731464691</v>
       </c>
-      <c r="M13" s="49">
+      <c r="M13" s="46">
         <f t="shared" si="3"/>
         <v>1465016.0201665794</v>
       </c>
-      <c r="N13" s="27">
+      <c r="N13" s="24">
         <f t="shared" si="3"/>
         <v>1709860.5526784095</v>
       </c>
-      <c r="P13" s="42" t="s">
+      <c r="P13" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="Q13" s="43"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="44"/>
+      <c r="Q13" s="40"/>
+      <c r="R13" s="40"/>
+      <c r="S13" s="41"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A14" s="64" t="s">
+      <c r="A14" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="65"/>
+      <c r="B14" s="62"/>
       <c r="C14" s="12">
         <v>1138501</v>
       </c>
-      <c r="E14" s="23"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="47"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="44"/>
       <c r="J14" s="11"/>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
       <c r="N14" s="12"/>
-      <c r="P14" s="32">
+      <c r="P14" s="29">
         <f>R11</f>
         <v>0.14920978355589787</v>
       </c>
-      <c r="Q14" s="73">
+      <c r="Q14" s="70">
         <v>8</v>
       </c>
-      <c r="R14" s="74">
+      <c r="R14" s="71">
         <v>9.7029274232086173</v>
       </c>
-      <c r="S14" s="75">
+      <c r="S14" s="72">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A15" s="66" t="s">
+      <c r="A15" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="67"/>
-      <c r="C15" s="27">
+      <c r="B15" s="64"/>
+      <c r="C15" s="24">
         <f>C13-C14</f>
         <v>3441781</v>
       </c>
-      <c r="E15" s="41" t="s">
+      <c r="E15" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="57"/>
-      <c r="G15" s="59">
+      <c r="F15" s="54"/>
+      <c r="G15" s="56">
         <v>2023</v>
       </c>
-      <c r="H15" s="60">
+      <c r="H15" s="57">
         <v>2024</v>
       </c>
-      <c r="I15" s="61">
+      <c r="I15" s="58">
         <v>2025</v>
       </c>
-      <c r="J15" s="60">
+      <c r="J15" s="57">
         <v>2026</v>
       </c>
-      <c r="K15" s="60">
+      <c r="K15" s="57">
         <v>2027</v>
       </c>
-      <c r="L15" s="60">
+      <c r="L15" s="57">
         <v>2028</v>
       </c>
-      <c r="M15" s="60">
+      <c r="M15" s="57">
         <v>2029</v>
       </c>
-      <c r="N15" s="61">
+      <c r="N15" s="58">
         <v>2030</v>
       </c>
-      <c r="P15" s="70">
+      <c r="P15" s="67">
         <v>0.2</v>
       </c>
       <c r="Q15" s="13">
-        <f t="dataTable" ref="Q15:S17" dt2D="1" dtr="1" r1="R5" r2="C21" ca="1"/>
+        <f t="dataTable" ref="Q15:S17" dt2D="1" dtr="1" r1="R5" r2="C21"/>
         <v>0.11352731866721943</v>
       </c>
       <c r="R15" s="13">
         <v>0.16484245656785856</v>
       </c>
-      <c r="S15" s="22">
+      <c r="S15" s="19">
         <v>0.1986163703929047</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="E16" s="62" t="s">
+      <c r="E16" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="F16" s="68"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="46"/>
-      <c r="I16" s="47">
+      <c r="F16" s="65"/>
+      <c r="G16" s="42"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="44">
         <f>I13</f>
         <v>1512311</v>
       </c>
-      <c r="J16" s="46">
+      <c r="J16" s="43">
         <f t="shared" ref="J16:N16" si="4">J13</f>
         <v>857149.71112547396</v>
       </c>
-      <c r="K16" s="46">
+      <c r="K16" s="43">
         <f t="shared" si="4"/>
         <v>1040313.0395303394</v>
       </c>
-      <c r="L16" s="46">
+      <c r="L16" s="43">
         <f t="shared" si="4"/>
         <v>1242404.6731464691</v>
       </c>
-      <c r="M16" s="46">
+      <c r="M16" s="43">
         <f t="shared" si="4"/>
         <v>1465016.0201665794</v>
       </c>
-      <c r="N16" s="47">
+      <c r="N16" s="44">
         <f t="shared" si="4"/>
         <v>1709860.5526784095</v>
       </c>
-      <c r="P16" s="71">
+      <c r="P16" s="68">
         <v>0.25</v>
       </c>
       <c r="Q16" s="13">
@@ -1578,21 +1582,21 @@
       <c r="R16" s="13">
         <v>0.14920978355589787</v>
       </c>
-      <c r="S16" s="22">
+      <c r="S16" s="19">
         <v>0.18253043733003804</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="42" t="s">
+      <c r="A17" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="43"/>
-      <c r="C17" s="44"/>
-      <c r="E17" s="64" t="s">
+      <c r="B17" s="40"/>
+      <c r="C17" s="41"/>
+      <c r="E17" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="69"/>
-      <c r="G17" s="34">
+      <c r="F17" s="66"/>
+      <c r="G17" s="31">
         <f>G8</f>
         <v>848793</v>
       </c>
@@ -1624,33 +1628,33 @@
         <f t="shared" si="5"/>
         <v>1283777.2944073423</v>
       </c>
-      <c r="P17" s="72">
+      <c r="P17" s="69">
         <v>0.3</v>
       </c>
-      <c r="Q17" s="25">
+      <c r="Q17" s="22">
         <v>8.4767271256493082E-2</v>
       </c>
-      <c r="R17" s="25">
+      <c r="R17" s="22">
         <v>0.1347570480508804</v>
       </c>
-      <c r="S17" s="26">
+      <c r="S17" s="23">
         <v>0.16765865335994246</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="62" t="s">
+      <c r="A18" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="63"/>
-      <c r="C18" s="28">
+      <c r="B18" s="60"/>
+      <c r="C18" s="25">
         <f>220226320</f>
         <v>220226320</v>
       </c>
-      <c r="E18" s="64" t="s">
+      <c r="E18" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="F18" s="69"/>
-      <c r="G18" s="34">
+      <c r="F18" s="66"/>
+      <c r="G18" s="31">
         <v>1700222</v>
       </c>
       <c r="H18" s="11">
@@ -1681,18 +1685,18 @@
       </c>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="65"/>
-      <c r="C19" s="29">
+      <c r="B19" s="62"/>
+      <c r="C19" s="26">
         <v>101.75</v>
       </c>
-      <c r="E19" s="64" t="s">
+      <c r="E19" s="61" t="s">
         <v>49</v>
       </c>
-      <c r="F19" s="69"/>
-      <c r="G19" s="34"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="31"/>
       <c r="H19" s="11">
         <v>2215092</v>
       </c>
@@ -1703,27 +1707,27 @@
       <c r="L19" s="11"/>
       <c r="M19" s="11"/>
       <c r="N19" s="12"/>
-      <c r="P19" s="42" t="s">
+      <c r="P19" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="Q19" s="43"/>
-      <c r="R19" s="43"/>
-      <c r="S19" s="44"/>
+      <c r="Q19" s="40"/>
+      <c r="R19" s="40"/>
+      <c r="S19" s="41"/>
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A20" s="64" t="s">
+      <c r="A20" s="61" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="65"/>
-      <c r="C20" s="17">
+      <c r="B20" s="62"/>
+      <c r="C20" s="16">
         <f>(C18*C19)/1000</f>
         <v>22408028.059999999</v>
       </c>
-      <c r="E20" s="64" t="s">
+      <c r="E20" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="F20" s="69"/>
-      <c r="G20" s="34"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="31"/>
       <c r="H20" s="11"/>
       <c r="I20" s="12">
         <f>I19-H19</f>
@@ -1749,33 +1753,33 @@
         <f>N$6*N30</f>
         <v>-1136754.4106006471</v>
       </c>
-      <c r="P20" s="32">
+      <c r="P20" s="29">
         <f>R11</f>
         <v>0.14920978355589787</v>
       </c>
-      <c r="Q20" s="73">
+      <c r="Q20" s="70">
         <v>8</v>
       </c>
-      <c r="R20" s="74">
+      <c r="R20" s="71">
         <v>9.7029274232086173</v>
       </c>
-      <c r="S20" s="75">
+      <c r="S20" s="72">
         <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="B21" s="35"/>
-      <c r="C21" s="30">
+      <c r="B21" s="32"/>
+      <c r="C21" s="27">
         <v>0.25</v>
       </c>
-      <c r="E21" s="64" t="s">
+      <c r="E21" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="F21" s="69"/>
-      <c r="G21" s="34"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="31"/>
       <c r="H21" s="11"/>
       <c r="I21" s="12"/>
       <c r="J21" s="11">
@@ -1798,57 +1802,57 @@
         <f t="shared" si="6"/>
         <v>2540099.7533835913</v>
       </c>
-      <c r="P21" s="76">
+      <c r="P21" s="73">
         <v>4</v>
       </c>
       <c r="Q21" s="13">
-        <f t="dataTable" ref="Q21:S24" dt2D="1" dtr="1" r1="R5" r2="C33"/>
+        <f t="dataTable" ref="Q21:S24" dt2D="1" dtr="1" r1="R5" r2="C33" ca="1"/>
         <v>9.6593263600101675E-2</v>
       </c>
       <c r="R21" s="13">
         <v>0.14356812953807596</v>
       </c>
-      <c r="S21" s="22">
+      <c r="S21" s="19">
         <v>0.17477597218318763</v>
       </c>
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="64" t="s">
+      <c r="A22" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="65"/>
-      <c r="C22" s="17">
+      <c r="B22" s="62"/>
+      <c r="C22" s="16">
         <f>C20*(1+C21)</f>
         <v>28010035.074999999</v>
       </c>
-      <c r="E22" s="85" t="s">
+      <c r="E22" s="82" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="98"/>
-      <c r="G22" s="100"/>
-      <c r="H22" s="101"/>
-      <c r="I22" s="102"/>
-      <c r="J22" s="103">
+      <c r="F22" s="95"/>
+      <c r="G22" s="97"/>
+      <c r="H22" s="98"/>
+      <c r="I22" s="99"/>
+      <c r="J22" s="100">
         <f>J21/J7</f>
         <v>0.45154204192528635</v>
       </c>
-      <c r="K22" s="103">
+      <c r="K22" s="100">
         <f t="shared" ref="K22:N22" si="7">K21/K7</f>
         <v>0.49054373278898505</v>
       </c>
-      <c r="L22" s="103">
+      <c r="L22" s="100">
         <f t="shared" si="7"/>
         <v>0.53021658113363146</v>
       </c>
-      <c r="M22" s="103">
+      <c r="M22" s="100">
         <f t="shared" si="7"/>
         <v>0.57056367976478162</v>
       </c>
-      <c r="N22" s="90">
+      <c r="N22" s="87">
         <f t="shared" si="7"/>
         <v>0.61158846615964824</v>
       </c>
-      <c r="P22" s="77">
+      <c r="P22" s="74">
         <v>4.5</v>
       </c>
       <c r="Q22" s="13">
@@ -1857,30 +1861,30 @@
       <c r="R22" s="13">
         <v>0.14920978355589787</v>
       </c>
-      <c r="S22" s="22">
+      <c r="S22" s="19">
         <v>0.18253043733003804</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="64" t="s">
+      <c r="A23" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="65"/>
-      <c r="C23" s="17">
+      <c r="B23" s="62"/>
+      <c r="C23" s="16">
         <f>C15</f>
         <v>3441781</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="7"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="38"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="35"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
       <c r="M23" s="7"/>
       <c r="N23" s="8"/>
-      <c r="P23" s="77">
+      <c r="P23" s="74">
         <v>5</v>
       </c>
       <c r="Q23" s="13">
@@ -1889,118 +1893,118 @@
       <c r="R23" s="13">
         <v>0.15585972116163371</v>
       </c>
-      <c r="S23" s="22">
+      <c r="S23" s="19">
         <v>0.19160636396669961</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="64" t="s">
+      <c r="A24" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="65"/>
-      <c r="C24" s="17">
+      <c r="B24" s="62"/>
+      <c r="C24" s="16">
         <f>C22+C23</f>
         <v>31451816.074999999</v>
       </c>
-      <c r="E24" s="41" t="s">
+      <c r="E24" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="57"/>
-      <c r="G24" s="59">
+      <c r="F24" s="54"/>
+      <c r="G24" s="56">
         <v>2023</v>
       </c>
-      <c r="H24" s="60">
+      <c r="H24" s="57">
         <v>2024</v>
       </c>
-      <c r="I24" s="61">
+      <c r="I24" s="58">
         <v>2025</v>
       </c>
-      <c r="J24" s="60">
+      <c r="J24" s="57">
         <v>2026</v>
       </c>
-      <c r="K24" s="60">
+      <c r="K24" s="57">
         <v>2027</v>
       </c>
-      <c r="L24" s="60">
+      <c r="L24" s="57">
         <v>2028</v>
       </c>
-      <c r="M24" s="60">
+      <c r="M24" s="57">
         <v>2029</v>
       </c>
-      <c r="N24" s="61">
+      <c r="N24" s="58">
         <v>2030</v>
       </c>
-      <c r="P24" s="78">
+      <c r="P24" s="75">
         <v>5.5</v>
       </c>
-      <c r="Q24" s="25">
+      <c r="Q24" s="22">
         <v>0.10385113955539049</v>
       </c>
-      <c r="R24" s="25">
+      <c r="R24" s="22">
         <v>0.16381830961984289</v>
       </c>
-      <c r="S24" s="26">
+      <c r="S24" s="23">
         <v>0.20238137093931674</v>
       </c>
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="64" t="s">
+      <c r="A25" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="65"/>
-      <c r="C25" s="17">
+      <c r="B25" s="62"/>
+      <c r="C25" s="16">
         <f>C9</f>
         <v>3241477</v>
       </c>
-      <c r="E25" s="62" t="s">
+      <c r="E25" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="F25" s="63"/>
+      <c r="F25" s="60"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="50">
+      <c r="H25" s="47">
         <f>(H6-G6)/G6</f>
         <v>4.9641228412082836E-2</v>
       </c>
-      <c r="I25" s="51">
+      <c r="I25" s="48">
         <f>(I6-H6)/H6</f>
         <v>5.2005441306118332E-2</v>
       </c>
-      <c r="J25" s="52">
+      <c r="J25" s="49">
         <f>AVERAGE($H25:$I25)</f>
         <v>5.082333485910058E-2</v>
       </c>
-      <c r="K25" s="52">
+      <c r="K25" s="49">
         <f>AVERAGE($H25:$I25)</f>
         <v>5.082333485910058E-2</v>
       </c>
-      <c r="L25" s="52">
+      <c r="L25" s="49">
         <f>AVERAGE($H25:$I25)</f>
         <v>5.082333485910058E-2</v>
       </c>
-      <c r="M25" s="52">
+      <c r="M25" s="49">
         <f>AVERAGE($H25:$I25)</f>
         <v>5.082333485910058E-2</v>
       </c>
-      <c r="N25" s="53">
+      <c r="N25" s="50">
         <f>AVERAGE($H25:$I25)</f>
         <v>5.082333485910058E-2</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A26" s="85" t="s">
+      <c r="A26" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="86"/>
-      <c r="C26" s="87">
+      <c r="B26" s="83"/>
+      <c r="C26" s="84">
         <f>C24/C25</f>
         <v>9.7029274232086173</v>
       </c>
-      <c r="E26" s="64" t="s">
+      <c r="E26" s="61" t="s">
         <v>39</v>
       </c>
-      <c r="F26" s="65"/>
+      <c r="F26" s="62"/>
       <c r="G26" s="9"/>
-      <c r="I26" s="22">
+      <c r="I26" s="19">
         <f>I7/I6</f>
         <v>7.5869511378857349E-2</v>
       </c>
@@ -2024,20 +2028,20 @@
         <f>M$26</f>
         <v>7.5869511378857349E-2</v>
       </c>
-      <c r="P26" s="42" t="s">
+      <c r="P26" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="44"/>
+      <c r="Q26" s="40"/>
+      <c r="R26" s="40"/>
+      <c r="S26" s="41"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="D27" s="3"/>
-      <c r="E27" s="64" t="s">
+      <c r="E27" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="F27" s="65"/>
-      <c r="G27" s="33">
+      <c r="F27" s="62"/>
+      <c r="G27" s="30">
         <f>G8/G6</f>
         <v>2.1937392161695834E-2</v>
       </c>
@@ -2045,7 +2049,7 @@
         <f>H8/H6</f>
         <v>2.3926318100414286E-2</v>
       </c>
-      <c r="I27" s="22">
+      <c r="I27" s="19">
         <f>I8/I6</f>
         <v>2.4489957944141903E-2</v>
       </c>
@@ -2069,32 +2073,32 @@
         <f>AVERAGE($G27:$I27)</f>
         <v>2.3451222735417342E-2</v>
       </c>
-      <c r="P27" s="32">
+      <c r="P27" s="29">
         <f>R11</f>
         <v>0.14920978355589787</v>
       </c>
-      <c r="Q27" s="79">
+      <c r="Q27" s="76">
         <v>0.2</v>
       </c>
-      <c r="R27" s="80">
+      <c r="R27" s="77">
         <v>0.25</v>
       </c>
-      <c r="S27" s="81">
+      <c r="S27" s="78">
         <v>0.3</v>
       </c>
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A28" s="42" t="s">
+      <c r="A28" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="43"/>
-      <c r="C28" s="44"/>
-      <c r="E28" s="64" t="s">
+      <c r="B28" s="40"/>
+      <c r="C28" s="41"/>
+      <c r="E28" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="F28" s="65"/>
+      <c r="F28" s="62"/>
       <c r="G28" s="9"/>
-      <c r="I28" s="22">
+      <c r="I28" s="19">
         <f>I12/I11</f>
         <v>0.23021624846278516</v>
       </c>
@@ -2118,7 +2122,7 @@
         <f>M$28</f>
         <v>0.23021624846278516</v>
       </c>
-      <c r="P28" s="76">
+      <c r="P28" s="73">
         <v>4</v>
       </c>
       <c r="Q28" s="13">
@@ -2128,24 +2132,24 @@
       <c r="R28" s="13">
         <v>0.14356812953807596</v>
       </c>
-      <c r="S28" s="22">
+      <c r="S28" s="19">
         <v>0.13891519238631078</v>
       </c>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="62" t="s">
+      <c r="A29" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="B29" s="63"/>
-      <c r="C29" s="17">
+      <c r="B29" s="60"/>
+      <c r="C29" s="16">
         <f>C24</f>
         <v>31451816.074999999</v>
       </c>
-      <c r="E29" s="64" t="s">
+      <c r="E29" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="F29" s="65"/>
-      <c r="G29" s="33">
+      <c r="F29" s="62"/>
+      <c r="G29" s="30">
         <f>G18/G6</f>
         <v>4.3942912790212472E-2</v>
       </c>
@@ -2153,7 +2157,7 @@
         <f>H18/H6</f>
         <v>3.2253473503648204E-2</v>
       </c>
-      <c r="I29" s="22">
+      <c r="I29" s="19">
         <f>I18/I6</f>
         <v>2.9050446596414332E-2</v>
       </c>
@@ -2173,11 +2177,11 @@
         <f t="shared" si="8"/>
         <v>2.9050446596414332E-2</v>
       </c>
-      <c r="N29" s="22">
+      <c r="N29" s="19">
         <f t="shared" si="8"/>
         <v>2.9050446596414332E-2</v>
       </c>
-      <c r="P29" s="77">
+      <c r="P29" s="74">
         <v>4.5</v>
       </c>
       <c r="Q29" s="13">
@@ -2186,49 +2190,49 @@
       <c r="R29" s="13">
         <v>0.14920978355589787</v>
       </c>
-      <c r="S29" s="22">
+      <c r="S29" s="19">
         <v>0.14389957560754829</v>
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B30" s="35"/>
-      <c r="C30" s="30">
+      <c r="B30" s="32"/>
+      <c r="C30" s="27">
         <v>0.02</v>
       </c>
-      <c r="E30" s="66" t="s">
+      <c r="E30" s="63" t="s">
         <v>51</v>
       </c>
-      <c r="F30" s="67"/>
-      <c r="G30" s="23"/>
-      <c r="H30" s="24"/>
-      <c r="I30" s="26">
+      <c r="F30" s="64"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="23">
         <f>I20/I6</f>
         <v>-2.0765502704089087E-2</v>
       </c>
-      <c r="J30" s="25">
+      <c r="J30" s="22">
         <f t="shared" si="8"/>
         <v>-2.0765502704089087E-2</v>
       </c>
-      <c r="K30" s="25">
+      <c r="K30" s="22">
         <f t="shared" si="8"/>
         <v>-2.0765502704089087E-2</v>
       </c>
-      <c r="L30" s="25">
+      <c r="L30" s="22">
         <f t="shared" si="8"/>
         <v>-2.0765502704089087E-2</v>
       </c>
-      <c r="M30" s="25">
+      <c r="M30" s="22">
         <f t="shared" si="8"/>
         <v>-2.0765502704089087E-2</v>
       </c>
-      <c r="N30" s="26">
+      <c r="N30" s="23">
         <f t="shared" si="8"/>
         <v>-2.0765502704089087E-2</v>
       </c>
-      <c r="P30" s="77">
+      <c r="P30" s="74">
         <v>5</v>
       </c>
       <c r="Q30" s="13">
@@ -2237,21 +2241,21 @@
       <c r="R30" s="13">
         <v>0.15585972116163371</v>
       </c>
-      <c r="S30" s="22">
+      <c r="S30" s="19">
         <v>0.1497223781312953</v>
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A31" s="64" t="s">
+      <c r="A31" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="65"/>
-      <c r="C31" s="17">
+      <c r="B31" s="62"/>
+      <c r="C31" s="16">
         <f>C29*(1+C30)</f>
         <v>32080852.396499999</v>
       </c>
-      <c r="E31" s="23"/>
-      <c r="F31" s="39"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="36"/>
       <c r="G31" s="9"/>
       <c r="I31" s="10"/>
       <c r="J31" s="6"/>
@@ -2259,84 +2263,84 @@
       <c r="L31" s="7"/>
       <c r="M31" s="7"/>
       <c r="N31" s="8"/>
-      <c r="P31" s="78">
+      <c r="P31" s="75">
         <v>5.5</v>
       </c>
-      <c r="Q31" s="25">
+      <c r="Q31" s="22">
         <v>0.17205380637822176</v>
       </c>
-      <c r="R31" s="25">
+      <c r="R31" s="22">
         <v>0.16381830961984289</v>
       </c>
-      <c r="S31" s="26">
+      <c r="S31" s="23">
         <v>0.15661692813409656</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A32" s="64"/>
-      <c r="B32" s="65"/>
+      <c r="A32" s="61"/>
+      <c r="B32" s="62"/>
       <c r="C32" s="10"/>
-      <c r="E32" s="56" t="s">
+      <c r="E32" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="F32" s="58"/>
-      <c r="G32" s="59">
+      <c r="F32" s="55"/>
+      <c r="G32" s="56">
         <v>2023</v>
       </c>
-      <c r="H32" s="60">
+      <c r="H32" s="57">
         <v>2024</v>
       </c>
-      <c r="I32" s="61">
+      <c r="I32" s="58">
         <v>2025</v>
       </c>
-      <c r="J32" s="60">
+      <c r="J32" s="57">
         <v>2026</v>
       </c>
-      <c r="K32" s="60">
+      <c r="K32" s="57">
         <v>2027</v>
       </c>
-      <c r="L32" s="60">
+      <c r="L32" s="57">
         <v>2028</v>
       </c>
-      <c r="M32" s="60">
+      <c r="M32" s="57">
         <v>2029</v>
       </c>
-      <c r="N32" s="61">
+      <c r="N32" s="58">
         <v>2030</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="35"/>
-      <c r="C33" s="31">
+      <c r="B33" s="32"/>
+      <c r="C33" s="28">
         <v>4.5</v>
       </c>
-      <c r="E33" s="62" t="s">
+      <c r="E33" s="59" t="s">
         <v>41</v>
       </c>
-      <c r="F33" s="68"/>
+      <c r="F33" s="65"/>
       <c r="G33" s="6"/>
       <c r="H33" s="7"/>
       <c r="I33" s="8"/>
-      <c r="J33" s="54">
+      <c r="J33" s="101">
         <f>C34</f>
         <v>14586646.5</v>
       </c>
-      <c r="K33" s="54">
+      <c r="K33" s="51">
         <f>J36</f>
         <v>13194461.579506487</v>
       </c>
-      <c r="L33" s="54">
+      <c r="L33" s="51">
         <f>K36</f>
         <v>11584507.636805579</v>
       </c>
-      <c r="M33" s="54">
+      <c r="M33" s="51">
         <f>L36</f>
         <v>9736097.5899218544</v>
       </c>
-      <c r="N33" s="55">
+      <c r="N33" s="52">
         <f>M36</f>
         <v>7626863.5617867485</v>
       </c>
@@ -2345,38 +2349,38 @@
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" s="82" t="s">
+      <c r="A34" s="79" t="s">
         <v>23</v>
       </c>
-      <c r="B34" s="83"/>
-      <c r="C34" s="84">
+      <c r="B34" s="80"/>
+      <c r="C34" s="81">
         <f>C9*C33</f>
         <v>14586646.5</v>
       </c>
-      <c r="E34" s="18" t="s">
+      <c r="E34" s="17" t="s">
         <v>70</v>
       </c>
       <c r="F34" s="5"/>
-      <c r="G34" s="18"/>
+      <c r="G34" s="17"/>
       <c r="H34" s="5"/>
-      <c r="I34" s="21"/>
-      <c r="J34" s="20">
+      <c r="I34" s="18"/>
+      <c r="J34" s="102">
         <f>C34*0.01</f>
         <v>145866.465</v>
       </c>
-      <c r="K34" s="16">
+      <c r="K34" s="103">
         <f>J34</f>
         <v>145866.465</v>
       </c>
-      <c r="L34" s="16">
+      <c r="L34" s="103">
         <f t="shared" ref="L34:N34" si="9">K34</f>
         <v>145866.465</v>
       </c>
-      <c r="M34" s="16">
+      <c r="M34" s="103">
         <f t="shared" si="9"/>
         <v>145866.465</v>
       </c>
-      <c r="N34" s="17">
+      <c r="N34" s="16">
         <f t="shared" si="9"/>
         <v>145866.465</v>
       </c>
@@ -2385,37 +2389,37 @@
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" s="82" t="s">
+      <c r="A35" s="79" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="83"/>
-      <c r="C35" s="84">
+      <c r="B35" s="80"/>
+      <c r="C35" s="81">
         <f>C31-C34</f>
         <v>17494205.896499999</v>
       </c>
-      <c r="E35" s="64" t="s">
+      <c r="E35" s="61" t="s">
         <v>69</v>
       </c>
-      <c r="F35" s="69"/>
+      <c r="F35" s="66"/>
       <c r="G35" s="9"/>
       <c r="I35" s="10"/>
-      <c r="J35" s="16">
+      <c r="J35" s="104">
         <f>J21-J34</f>
         <v>1392184.9204935138</v>
       </c>
-      <c r="K35" s="16">
+      <c r="K35" s="103">
         <f t="shared" ref="K35:N35" si="10">K21-K34</f>
         <v>1609953.9427009083</v>
       </c>
-      <c r="L35" s="16">
+      <c r="L35" s="103">
         <f t="shared" si="10"/>
         <v>1848410.0468837244</v>
       </c>
-      <c r="M35" s="16">
+      <c r="M35" s="103">
         <f t="shared" si="10"/>
         <v>2109234.028135106</v>
       </c>
-      <c r="N35" s="17">
+      <c r="N35" s="16">
         <f t="shared" si="10"/>
         <v>2394233.2883835915</v>
       </c>
@@ -2424,33 +2428,33 @@
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" s="64" t="s">
+      <c r="A36" s="61" t="s">
         <v>27</v>
       </c>
-      <c r="B36" s="65"/>
-      <c r="C36" s="17">
+      <c r="B36" s="62"/>
+      <c r="C36" s="16">
         <f>C34+C35</f>
         <v>32080852.396499999</v>
       </c>
-      <c r="E36" s="64" t="s">
+      <c r="E36" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="F36" s="69"/>
+      <c r="F36" s="66"/>
       <c r="G36" s="9"/>
       <c r="I36" s="10"/>
-      <c r="J36" s="16">
+      <c r="J36" s="104">
         <f>MAX(J33-J35,0)</f>
         <v>13194461.579506487</v>
       </c>
-      <c r="K36" s="16">
+      <c r="K36" s="103">
         <f t="shared" ref="K36:N36" si="11">MAX(K33-K35,0)</f>
         <v>11584507.636805579</v>
       </c>
-      <c r="L36" s="16">
+      <c r="L36" s="103">
         <f t="shared" si="11"/>
         <v>9736097.5899218544</v>
       </c>
-      <c r="M36" s="16">
+      <c r="M36" s="103">
         <f t="shared" si="11"/>
         <v>7626863.5617867485</v>
       </c>
@@ -2463,71 +2467,71 @@
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" s="85" t="s">
+      <c r="A37" s="82" t="s">
         <v>28</v>
       </c>
-      <c r="B37" s="86"/>
-      <c r="C37" s="88">
+      <c r="B37" s="83"/>
+      <c r="C37" s="85">
         <f>C34/C36</f>
         <v>0.4546838818282582</v>
       </c>
-      <c r="E37" s="18" t="s">
+      <c r="E37" s="17" t="s">
         <v>40</v>
       </c>
       <c r="F37" s="5"/>
-      <c r="G37" s="18"/>
+      <c r="G37" s="17"/>
       <c r="H37" s="5"/>
-      <c r="I37" s="35"/>
-      <c r="J37" s="19">
+      <c r="I37" s="32"/>
+      <c r="J37" s="105">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="K37" s="19">
+      <c r="K37" s="106">
         <f>$J37</f>
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="L37" s="19">
+      <c r="L37" s="106">
         <f>$J37</f>
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="M37" s="19">
+      <c r="M37" s="106">
         <f>$J37</f>
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="N37" s="21">
+      <c r="N37" s="18">
         <f>$J37</f>
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="P37" s="91" t="s">
+      <c r="P37" s="88" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E38" s="64" t="s">
+      <c r="E38" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="F38" s="69"/>
-      <c r="G38" s="97"/>
-      <c r="I38" s="17">
+      <c r="F38" s="66"/>
+      <c r="G38" s="94"/>
+      <c r="I38" s="16">
         <f>I10</f>
         <v>230567</v>
       </c>
-      <c r="J38" s="16">
+      <c r="J38" s="104">
         <f>J33*J37</f>
         <v>1239864.9525000001</v>
       </c>
-      <c r="K38" s="16">
+      <c r="K38" s="103">
         <f>K33*K37</f>
         <v>1121529.2342580515</v>
       </c>
-      <c r="L38" s="16">
+      <c r="L38" s="103">
         <f>L33*L37</f>
         <v>984683.1491284743</v>
       </c>
-      <c r="M38" s="16">
+      <c r="M38" s="103">
         <f>M33*M37</f>
         <v>827568.29514335771</v>
       </c>
-      <c r="N38" s="17">
+      <c r="N38" s="16">
         <f>N33*N37</f>
         <v>648283.40275187371</v>
       </c>
@@ -2536,30 +2540,30 @@
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="E39" s="85" t="s">
+      <c r="E39" s="82" t="s">
         <v>67</v>
       </c>
-      <c r="F39" s="98"/>
-      <c r="G39" s="85"/>
-      <c r="H39" s="98"/>
-      <c r="I39" s="86"/>
-      <c r="J39" s="99">
+      <c r="F39" s="95"/>
+      <c r="G39" s="82"/>
+      <c r="H39" s="95"/>
+      <c r="I39" s="83"/>
+      <c r="J39" s="107">
         <f>J7/J38</f>
         <v>2.7472505486512433</v>
       </c>
-      <c r="K39" s="99">
+      <c r="K39" s="96">
         <f t="shared" ref="K39:N39" si="12">K7/K38</f>
         <v>3.1914773191983121</v>
       </c>
-      <c r="L39" s="99">
+      <c r="L39" s="96">
         <f t="shared" si="12"/>
         <v>3.819755486169107</v>
       </c>
-      <c r="M39" s="99">
+      <c r="M39" s="96">
         <f t="shared" si="12"/>
         <v>4.7759297867848067</v>
       </c>
-      <c r="N39" s="87">
+      <c r="N39" s="84">
         <f t="shared" si="12"/>
         <v>6.4065848557205332</v>
       </c>
